--- a/exports/trend_1d/GMRAIRPORT_full_report.xlsx
+++ b/exports/trend_1d/GMRAIRPORT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.13</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>17.64</v>
+        <v>16.95</v>
       </c>
       <c r="I2" t="n">
         <v>17.3555549847664</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>1.44</v>
+        <v>-2.53</v>
       </c>
       <c r="L2" t="n">
         <v>5.12</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>21.48</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42100</v>
+        <v>42101</v>
       </c>
       <c r="H3" t="n">
-        <v>16.89</v>
+        <v>17.7</v>
       </c>
       <c r="I3" t="n">
         <v>17.2504528983597</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>0.35</v>
+        <v>-4.42</v>
       </c>
       <c r="L3" t="n">
         <v>16.52</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>15.2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="I4" t="n">
         <v>16.26993102627123</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.78</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>8.470000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="M4" t="n">
         <v>4.94</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>17.51</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42179</v>
+        <v>42180</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>15.25</v>
       </c>
       <c r="I5" t="n">
         <v>14.63761944510344</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>13.04</v>
+        <v>5.28</v>
       </c>
       <c r="L5" t="n">
         <v>4.04</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>19.95</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H6" t="n">
-        <v>13.55</v>
+        <v>13.3</v>
       </c>
       <c r="I6" t="n">
         <v>13.39439452259342</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.15</v>
+        <v>-12.79</v>
       </c>
       <c r="L6" t="n">
-        <v>13.11</v>
+        <v>13.44</v>
       </c>
       <c r="M6" t="n">
         <v>4.81</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42269</v>
+        <v>42270</v>
       </c>
       <c r="H7" t="n">
-        <v>12.75</v>
+        <v>13.45</v>
       </c>
       <c r="I7" t="n">
         <v>13.23367834855875</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="L7" t="n">
         <v>4.14</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2.26</v>
       </c>
       <c r="M7" t="n">
         <v>3.77</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>19.41</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H8" t="n">
-        <v>12.6</v>
+        <v>12.05</v>
       </c>
       <c r="I8" t="n">
         <v>12.54018551207931</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.32</v>
+        <v>-10.41</v>
       </c>
       <c r="L8" t="n">
-        <v>7.43</v>
+        <v>10.78</v>
       </c>
       <c r="M8" t="n">
         <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>4.37</v>
       </c>
       <c r="O8" t="n">
         <v>5.49</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>16.12</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42321</v>
+        <v>42324</v>
       </c>
       <c r="H9" t="n">
-        <v>11.9</v>
+        <v>13.4</v>
       </c>
       <c r="I9" t="n">
         <v>13.33959002775542</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>1.24</v>
+        <v>-11.2</v>
       </c>
       <c r="L9" t="n">
-        <v>4.98</v>
+        <v>12.86</v>
       </c>
       <c r="M9" t="n">
-        <v>0.86</v>
+        <v>3.36</v>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>12.61</v>
       </c>
       <c r="O9" t="n">
         <v>-4.37</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>18.14</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H10" t="n">
-        <v>15.35</v>
+        <v>14.95</v>
       </c>
       <c r="I10" t="n">
         <v>15.31930643871014</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>14.55</v>
+        <v>11.57</v>
       </c>
       <c r="L10" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.63</v>
+        <v>1.3</v>
       </c>
       <c r="N10" t="n">
         <v>14.64</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>23.75</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42488</v>
+        <v>42489</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="I11" t="n">
         <v>12.59455448944422</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K11" t="n">
-        <v>19.73</v>
+        <v>15.72</v>
       </c>
       <c r="L11" t="n">
         <v>12.04</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>12.09</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42509</v>
+        <v>42510</v>
       </c>
       <c r="H12" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="I12" t="n">
         <v>11.32427844280307</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.130000000000001</v>
+        <v>-10.71</v>
       </c>
       <c r="L12" t="n">
-        <v>9.92</v>
+        <v>11.11</v>
       </c>
       <c r="M12" t="n">
         <v>0.85</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>12.4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42531</v>
+        <v>42534</v>
       </c>
       <c r="H13" t="n">
-        <v>12.1</v>
+        <v>12.35</v>
       </c>
       <c r="I13" t="n">
         <v>12.1303049987536</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.56</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>9.779999999999999</v>
+        <v>12.89</v>
       </c>
       <c r="M13" t="n">
         <v>3.48</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.78</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H14" t="n">
-        <v>13.75</v>
+        <v>12.35</v>
       </c>
       <c r="I14" t="n">
         <v>13.12605248316179</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K14" t="n">
-        <v>11.34</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>6.48</v>
@@ -1239,7 +1406,7 @@
         <v>5.98</v>
       </c>
       <c r="N14" t="n">
-        <v>6.79</v>
+        <v>10.18</v>
       </c>
       <c r="O14" t="n">
         <v>2.07</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>21.42</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H15" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="I15" t="n">
         <v>12.4140799177964</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.24</v>
       </c>
       <c r="L15" t="n">
         <v>16.6</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.71</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H16" t="n">
-        <v>16.8</v>
+        <v>15.9</v>
       </c>
       <c r="I16" t="n">
         <v>16.02049095097071</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K16" t="n">
-        <v>31.76</v>
+        <v>24.71</v>
       </c>
       <c r="L16" t="n">
         <v>3.92</v>
@@ -1353,7 +1544,7 @@
         <v>2.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.92</v>
+        <v>5.36</v>
       </c>
       <c r="O16" t="n">
         <v>4.08</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>16.11</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42895</v>
+        <v>42898</v>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>17.75</v>
       </c>
       <c r="I17" t="n">
         <v>17.47267062017042</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.92</v>
+        <v>-11.64</v>
       </c>
       <c r="L17" t="n">
         <v>19.81</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>19.93</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H18" t="n">
-        <v>17.7</v>
+        <v>16.95</v>
       </c>
       <c r="I18" t="n">
         <v>17.59510875272326</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.28</v>
+        <v>-4.51</v>
       </c>
       <c r="L18" t="n">
-        <v>5.63</v>
+        <v>6.2</v>
       </c>
       <c r="M18" t="n">
         <v>3.06</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>16.68</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H19" t="n">
-        <v>17.4</v>
+        <v>18.45</v>
       </c>
       <c r="I19" t="n">
         <v>17.66462416326013</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.65</v>
+        <v>-8.85</v>
       </c>
       <c r="L19" t="n">
         <v>12.98</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>13.12</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H20" t="n">
-        <v>17.85</v>
+        <v>16.35</v>
       </c>
       <c r="I20" t="n">
         <v>17.01088407099283</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.25</v>
+        <v>-11.38</v>
       </c>
       <c r="L20" t="n">
-        <v>6.23</v>
+        <v>15.18</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="N20" t="n">
-        <v>4.89</v>
+        <v>8.4</v>
       </c>
       <c r="O20" t="n">
         <v>6.03</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>18.38</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H21" t="n">
-        <v>18.3</v>
+        <v>19.85</v>
       </c>
       <c r="I21" t="n">
         <v>19.0004846338787</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.93</v>
+        <v>-21.41</v>
       </c>
       <c r="L21" t="n">
-        <v>19.88</v>
+        <v>26.3</v>
       </c>
       <c r="M21" t="n">
         <v>1.85</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>16</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H22" t="n">
-        <v>22.75</v>
+        <v>19.25</v>
       </c>
       <c r="I22" t="n">
         <v>19.51670784335609</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K22" t="n">
-        <v>14.61</v>
+        <v>-3.02</v>
       </c>
       <c r="L22" t="n">
-        <v>7.81</v>
+        <v>10.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0.66</v>
+        <v>1.54</v>
       </c>
       <c r="N22" t="n">
-        <v>5.6</v>
+        <v>15.38</v>
       </c>
       <c r="O22" t="n">
         <v>8.470000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>31.6</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43195</v>
+        <v>43196</v>
       </c>
       <c r="H23" t="n">
-        <v>18.85</v>
+        <v>20.1</v>
       </c>
       <c r="I23" t="n">
         <v>19.34206201760557</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K23" t="n">
-        <v>2.08</v>
+        <v>-4.42</v>
       </c>
       <c r="L23" t="n">
         <v>16.36</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>18.02</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H24" t="n">
-        <v>18.65</v>
+        <v>18.1</v>
       </c>
       <c r="I24" t="n">
         <v>18.10195743617383</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.21</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>8.710000000000001</v>
+        <v>11.19</v>
       </c>
       <c r="M24" t="n">
         <v>0.98</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>13.82</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43292</v>
+        <v>43293</v>
       </c>
       <c r="H25" t="n">
-        <v>17.05</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
         <v>17.50772630815199</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K25" t="n">
-        <v>5.8</v>
+        <v>0.55</v>
       </c>
       <c r="L25" t="n">
         <v>4.14</v>
       </c>
       <c r="M25" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>5.57</v>
       </c>
       <c r="O25" t="n">
         <v>-2.95</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.1</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43360</v>
+        <v>43361</v>
       </c>
       <c r="H26" t="n">
-        <v>18.45</v>
+        <v>17.7</v>
       </c>
       <c r="I26" t="n">
         <v>17.97554397077278</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>-1.67</v>
       </c>
       <c r="L26" t="n">
         <v>5</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>17.66</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43473</v>
+        <v>43474</v>
       </c>
       <c r="H27" t="n">
-        <v>16.05</v>
+        <v>16.85</v>
       </c>
       <c r="I27" t="n">
         <v>16.45476266536779</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K27" t="n">
-        <v>9.32</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
         <v>5.65</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43495</v>
+        <v>43496</v>
       </c>
       <c r="H28" t="n">
-        <v>15.55</v>
+        <v>15.2</v>
       </c>
       <c r="I28" t="n">
         <v>15.2556685700825</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.72</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>10.98</v>
@@ -2037,7 +2372,7 @@
         <v>0.97</v>
       </c>
       <c r="N28" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
         <v>4.98</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.7</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43517</v>
+        <v>43518</v>
       </c>
       <c r="H29" t="n">
-        <v>16.15</v>
+        <v>16.45</v>
       </c>
       <c r="I29" t="n">
         <v>16.21371355309218</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.25</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>6.91</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>1.69</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H30" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="I30" t="n">
         <v>17.5513436533501</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K30" t="n">
-        <v>8.210000000000001</v>
+        <v>5.78</v>
       </c>
       <c r="L30" t="n">
         <v>3.34</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.76</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43693</v>
+        <v>43696</v>
       </c>
       <c r="H31" t="n">
-        <v>15.25</v>
+        <v>15.9</v>
       </c>
       <c r="I31" t="n">
         <v>15.70380322307029</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K31" t="n">
-        <v>12.36</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L31" t="n">
         <v>3.45</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.13</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H32" t="n">
-        <v>22.85</v>
+        <v>21.3</v>
       </c>
       <c r="I32" t="n">
         <v>21.64938788924055</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K32" t="n">
-        <v>43.71</v>
+        <v>33.96</v>
       </c>
       <c r="L32" t="n">
         <v>9.119999999999999</v>
@@ -2265,7 +2648,7 @@
         <v>2.28</v>
       </c>
       <c r="N32" t="n">
-        <v>4.72</v>
+        <v>6.78</v>
       </c>
       <c r="O32" t="n">
         <v>4.26</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>17.02</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H33" t="n">
-        <v>23.65</v>
+        <v>25.45</v>
       </c>
       <c r="I33" t="n">
         <v>24.19264125075411</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.03</v>
+        <v>-19.48</v>
       </c>
       <c r="L33" t="n">
-        <v>12.68</v>
+        <v>24.41</v>
       </c>
       <c r="M33" t="n">
-        <v>1.77</v>
+        <v>9.94</v>
       </c>
       <c r="N33" t="n">
-        <v>4.09</v>
+        <v>7.61</v>
       </c>
       <c r="O33" t="n">
         <v>-6.78</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.7</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H34" t="n">
-        <v>22.8</v>
+        <v>20</v>
       </c>
       <c r="I34" t="n">
         <v>22.7453595887552</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.41</v>
+        <v>-21.41</v>
       </c>
       <c r="L34" t="n">
-        <v>11</v>
+        <v>22.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0.39</v>
+        <v>5.04</v>
       </c>
       <c r="N34" t="n">
-        <v>6.56</v>
+        <v>12.28</v>
       </c>
       <c r="O34" t="n">
         <v>7.61</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>23.93</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="H35" t="n">
-        <v>17.8</v>
+        <v>18.95</v>
       </c>
       <c r="I35" t="n">
         <v>18.6698934735573</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" t="n">
-        <v>11</v>
+        <v>5.25</v>
       </c>
       <c r="L35" t="n">
         <v>8.5</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.97</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H36" t="n">
-        <v>23.05</v>
+        <v>21.75</v>
       </c>
       <c r="I36" t="n">
         <v>22.38062023419231</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K36" t="n">
-        <v>21.64</v>
+        <v>14.78</v>
       </c>
       <c r="L36" t="n">
         <v>8.970000000000001</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>17.37</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44152</v>
+        <v>44153</v>
       </c>
       <c r="H37" t="n">
-        <v>24.35</v>
+        <v>25.6</v>
       </c>
       <c r="I37" t="n">
         <v>24.72524827473655</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.95</v>
+        <v>-17.7</v>
       </c>
       <c r="L37" t="n">
-        <v>16.78</v>
+        <v>18.62</v>
       </c>
       <c r="M37" t="n">
         <v>2.6</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>11.63</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H38" t="n">
-        <v>26.85</v>
+        <v>24.5</v>
       </c>
       <c r="I38" t="n">
         <v>24.93398006775505</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K38" t="n">
-        <v>4.88</v>
+        <v>-4.3</v>
       </c>
       <c r="L38" t="n">
-        <v>4.69</v>
+        <v>5.86</v>
       </c>
       <c r="M38" t="n">
         <v>1.17</v>
       </c>
       <c r="N38" t="n">
-        <v>3.21</v>
+        <v>8.75</v>
       </c>
       <c r="O38" t="n">
         <v>5.13</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>20.88</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44257</v>
+        <v>44258</v>
       </c>
       <c r="H39" t="n">
-        <v>27.6</v>
+        <v>27.75</v>
       </c>
       <c r="I39" t="n">
         <v>27.66186164700197</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.65</v>
+        <v>-13.27</v>
       </c>
       <c r="L39" t="n">
-        <v>15.51</v>
+        <v>16.73</v>
       </c>
       <c r="M39" t="n">
         <v>2.27</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.99</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H40" t="n">
-        <v>24.75</v>
+        <v>23.9</v>
       </c>
       <c r="I40" t="n">
         <v>24.70156016076033</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>-10.81</v>
+        <v>-13.87</v>
       </c>
       <c r="L40" t="n">
-        <v>11.53</v>
+        <v>15.32</v>
       </c>
       <c r="M40" t="n">
         <v>1.62</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>17.03</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H41" t="n">
-        <v>24.9</v>
+        <v>25.55</v>
       </c>
       <c r="I41" t="n">
         <v>25.31392071433136</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.18</v>
+        <v>-6.9</v>
       </c>
       <c r="L41" t="n">
         <v>11.3</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>12.23</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44400</v>
+        <v>44403</v>
       </c>
       <c r="H42" t="n">
-        <v>29</v>
+        <v>28.25</v>
       </c>
       <c r="I42" t="n">
         <v>28.34862535754235</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K42" t="n">
-        <v>13.5</v>
+        <v>10.57</v>
       </c>
       <c r="L42" t="n">
         <v>4.31</v>
       </c>
       <c r="M42" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="N42" t="n">
         <v>3.47</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.32</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44442</v>
+        <v>44445</v>
       </c>
       <c r="H43" t="n">
-        <v>30.45</v>
+        <v>30.85</v>
       </c>
       <c r="I43" t="n">
         <v>30.57351515890833</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.79</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>9.73</v>
+        <v>11.5</v>
       </c>
       <c r="M43" t="n">
         <v>1.45</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H44" t="n">
-        <v>39.25</v>
+        <v>37.45</v>
       </c>
       <c r="I44" t="n">
         <v>37.88879632916219</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K44" t="n">
-        <v>27.23</v>
+        <v>21.39</v>
       </c>
       <c r="L44" t="n">
         <v>4.05</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7</v>
+        <v>1.15</v>
       </c>
       <c r="N44" t="n">
-        <v>3.86</v>
+        <v>4.59</v>
       </c>
       <c r="O44" t="n">
         <v>1.31</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>14.89</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44538</v>
+        <v>44539</v>
       </c>
       <c r="H45" t="n">
-        <v>42.6</v>
+        <v>43.85</v>
       </c>
       <c r="I45" t="n">
         <v>43.02801153308148</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K45" t="n">
-        <v>-13.75</v>
+        <v>-17.09</v>
       </c>
       <c r="L45" t="n">
-        <v>16.42</v>
+        <v>18.69</v>
       </c>
       <c r="M45" t="n">
         <v>1.52</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.54</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H46" t="n">
-        <v>42.3</v>
+        <v>39.95</v>
       </c>
       <c r="I46" t="n">
         <v>41.80361711019999</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.53</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>12.09</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>19.71</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44656</v>
+        <v>44657</v>
       </c>
       <c r="H47" t="n">
-        <v>39.5</v>
+        <v>40.9</v>
       </c>
       <c r="I47" t="n">
         <v>40.22802222465191</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K47" t="n">
-        <v>1.13</v>
+        <v>-2.38</v>
       </c>
       <c r="L47" t="n">
         <v>11.39</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>12.59</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H48" t="n">
-        <v>37.75</v>
+        <v>36.1</v>
       </c>
       <c r="I48" t="n">
         <v>36.2720067631361</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.7</v>
+        <v>-11.74</v>
       </c>
       <c r="L48" t="n">
-        <v>11</v>
+        <v>12.84</v>
       </c>
       <c r="M48" t="n">
         <v>1.33</v>
       </c>
       <c r="N48" t="n">
-        <v>3.76</v>
+        <v>4.37</v>
       </c>
       <c r="O48" t="n">
         <v>3.54</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>13.34</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44704</v>
+        <v>44705</v>
       </c>
       <c r="H49" t="n">
-        <v>36.65</v>
+        <v>37</v>
       </c>
       <c r="I49" t="n">
         <v>36.84319174728555</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.52</v>
+        <v>-2.49</v>
       </c>
       <c r="L49" t="n">
         <v>5.12</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>11.36</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H50" t="n">
-        <v>35.85</v>
+        <v>34.3</v>
       </c>
       <c r="I50" t="n">
         <v>34.60960128531988</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.11</v>
+        <v>-7.3</v>
       </c>
       <c r="L50" t="n">
-        <v>4.59</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M50" t="n">
         <v>1.47</v>
       </c>
       <c r="N50" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="O50" t="n">
         <v>0.95</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>14.48</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H51" t="n">
-        <v>35.45</v>
+        <v>37.5</v>
       </c>
       <c r="I51" t="n">
         <v>37.2388687398002</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.35</v>
+        <v>-9.33</v>
       </c>
       <c r="L51" t="n">
-        <v>6.27</v>
+        <v>10.93</v>
       </c>
       <c r="M51" t="n">
         <v>1.67</v>
       </c>
       <c r="N51" t="n">
-        <v>4.94</v>
+        <v>5.78</v>
       </c>
       <c r="O51" t="n">
         <v>-4.32</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.94</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H52" t="n">
-        <v>37.2</v>
+        <v>35.6</v>
       </c>
       <c r="I52" t="n">
         <v>36.9823838827332</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.8</v>
+        <v>-5.07</v>
       </c>
       <c r="L52" t="n">
         <v>11.07</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.14</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44868</v>
+        <v>44869</v>
       </c>
       <c r="H53" t="n">
-        <v>37.45</v>
+        <v>38.05</v>
       </c>
       <c r="I53" t="n">
         <v>37.63609903700724</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.2</v>
+        <v>-6.88</v>
       </c>
       <c r="L53" t="n">
         <v>8.85</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.49</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H54" t="n">
-        <v>40</v>
+        <v>37.8</v>
       </c>
       <c r="I54" t="n">
         <v>39.99851365190586</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K54" t="n">
-        <v>5.12</v>
+        <v>-0.66</v>
       </c>
       <c r="L54" t="n">
         <v>6.44</v>
       </c>
       <c r="M54" t="n">
-        <v>0.47</v>
+        <v>1.5</v>
       </c>
       <c r="N54" t="n">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="O54" t="n">
         <v>1.6</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>14.62</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H55" t="n">
-        <v>39.45</v>
+        <v>41.35</v>
       </c>
       <c r="I55" t="n">
         <v>39.96135003433594</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.37</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>9.390000000000001</v>
+        <v>11.24</v>
       </c>
       <c r="M55" t="n">
         <v>1.48</v>
       </c>
       <c r="N55" t="n">
-        <v>3.65</v>
+        <v>4.82</v>
       </c>
       <c r="O55" t="n">
         <v>-5.5</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>9.1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45008</v>
+        <v>45009</v>
       </c>
       <c r="H56" t="n">
-        <v>39.45</v>
+        <v>38.75</v>
       </c>
       <c r="I56" t="n">
         <v>38.8581181396544</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.59</v>
+        <v>-6.29</v>
       </c>
       <c r="L56" t="n">
-        <v>4.96</v>
+        <v>6.65</v>
       </c>
       <c r="M56" t="n">
         <v>0.5</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>10.17</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H57" t="n">
-        <v>40.55</v>
+        <v>43.45</v>
       </c>
       <c r="I57" t="n">
         <v>41.20102968896954</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.65</v>
+        <v>-12.13</v>
       </c>
       <c r="L57" t="n">
-        <v>5.03</v>
+        <v>12.77</v>
       </c>
       <c r="M57" t="n">
         <v>0.53</v>
       </c>
       <c r="N57" t="n">
-        <v>4.53</v>
+        <v>7.15</v>
       </c>
       <c r="O57" t="n">
         <v>-1.77</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>13.08</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45072</v>
+        <v>45075</v>
       </c>
       <c r="H58" t="n">
-        <v>45</v>
+        <v>40.55</v>
       </c>
       <c r="I58" t="n">
         <v>43.63503362777594</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K58" t="n">
-        <v>3.57</v>
+        <v>-6.67</v>
       </c>
       <c r="L58" t="n">
-        <v>6.56</v>
+        <v>7.94</v>
       </c>
       <c r="M58" t="n">
-        <v>0.92</v>
+        <v>1.56</v>
       </c>
       <c r="N58" t="n">
-        <v>1.83</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O58" t="n">
         <v>7.15</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>13.85</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="H59" t="n">
-        <v>43.8</v>
+        <v>44.7</v>
       </c>
       <c r="I59" t="n">
         <v>44.59890509386604</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.01</v>
+        <v>-10.23</v>
       </c>
       <c r="L59" t="n">
-        <v>9.25</v>
+        <v>10.48</v>
       </c>
       <c r="M59" t="n">
         <v>1.2</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.83</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45217</v>
+        <v>45218</v>
       </c>
       <c r="H60" t="n">
-        <v>57.8</v>
+        <v>56.65</v>
       </c>
       <c r="I60" t="n">
         <v>57.70784585972106</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K60" t="n">
-        <v>29.31</v>
+        <v>26.73</v>
       </c>
       <c r="L60" t="n">
         <v>2.57</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H61" t="n">
-        <v>57.6</v>
+        <v>58.7</v>
       </c>
       <c r="I61" t="n">
         <v>58.41314758970702</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.68</v>
+        <v>-3.62</v>
       </c>
       <c r="L61" t="n">
-        <v>4.85</v>
+        <v>5.03</v>
       </c>
       <c r="M61" t="n">
         <v>1.38</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.06</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H62" t="n">
-        <v>80.95</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="I62" t="n">
         <v>79.92086369181874</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K62" t="n">
-        <v>37.9</v>
+        <v>28.02</v>
       </c>
       <c r="L62" t="n">
         <v>3.92</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>17.33</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H63" t="n">
-        <v>83.55</v>
+        <v>85</v>
       </c>
       <c r="I63" t="n">
         <v>84.82152795987302</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.18</v>
+        <v>-13.11</v>
       </c>
       <c r="L63" t="n">
-        <v>11.78</v>
+        <v>13.91</v>
       </c>
       <c r="M63" t="n">
         <v>2.97</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>11.2</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H64" t="n">
-        <v>83.3</v>
+        <v>79</v>
       </c>
       <c r="I64" t="n">
         <v>80.35232430744566</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K64" t="n">
-        <v>-2</v>
+        <v>-7.06</v>
       </c>
       <c r="L64" t="n">
         <v>7.94</v>
@@ -4089,7 +4856,7 @@
         <v>2.75</v>
       </c>
       <c r="N64" t="n">
-        <v>3.69</v>
+        <v>5.16</v>
       </c>
       <c r="O64" t="n">
         <v>1.74</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>16.7</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H65" t="n">
-        <v>91.73</v>
+        <v>93.92</v>
       </c>
       <c r="I65" t="n">
         <v>93.84754156551361</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K65" t="n">
-        <v>-16.11</v>
+        <v>-18.89</v>
       </c>
       <c r="L65" t="n">
-        <v>18.01</v>
+        <v>19.68</v>
       </c>
       <c r="M65" t="n">
         <v>5.02</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>14.92</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H66" t="n">
-        <v>95.77</v>
+        <v>91.03</v>
       </c>
       <c r="I66" t="n">
         <v>91.88455617643005</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K66" t="n">
-        <v>1.97</v>
+        <v>-3.08</v>
       </c>
       <c r="L66" t="n">
         <v>5.53</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>12.14</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H67" t="n">
-        <v>84.03</v>
+        <v>84.5</v>
       </c>
       <c r="I67" t="n">
         <v>84.18249094342889</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K67" t="n">
-        <v>7.69</v>
+        <v>7.17</v>
       </c>
       <c r="L67" t="n">
         <v>7.91</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.05</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H68" t="n">
-        <v>80.63</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="I68" t="n">
         <v>79.3998911754139</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.58</v>
+        <v>-6.72</v>
       </c>
       <c r="L68" t="n">
-        <v>5.09</v>
+        <v>7.69</v>
       </c>
       <c r="M68" t="n">
         <v>2.37</v>
       </c>
       <c r="N68" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="O68" t="n">
         <v>0.5600000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H69" t="n">
-        <v>74.95</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>75.34769771638921</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K69" t="n">
-        <v>4.91</v>
+        <v>2.72</v>
       </c>
       <c r="L69" t="n">
         <v>3.53</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.57</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H70" t="n">
-        <v>81.91</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I70" t="n">
         <v>81.9039253997754</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K70" t="n">
-        <v>6.82</v>
+        <v>5.5</v>
       </c>
       <c r="L70" t="n">
         <v>2.46</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>7.7</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="H71" t="n">
-        <v>86.01000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>87.13274079624895</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.32</v>
+        <v>-9.27</v>
       </c>
       <c r="L71" t="n">
-        <v>6.92</v>
+        <v>9.77</v>
       </c>
       <c r="M71" t="n">
         <v>1.11</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.47</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H72" t="n">
-        <v>90.63</v>
+        <v>89.19</v>
       </c>
       <c r="I72" t="n">
         <v>89.32502121830815</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K72" t="n">
-        <v>2.52</v>
+        <v>0.89</v>
       </c>
       <c r="L72" t="n">
         <v>2.48</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>8.42</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H73" t="n">
-        <v>89.17</v>
+        <v>92.84</v>
       </c>
       <c r="I73" t="n">
         <v>91.41133278547807</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K73" t="n">
-        <v>0.02</v>
+        <v>-4.09</v>
       </c>
       <c r="L73" t="n">
-        <v>2.8</v>
+        <v>4.73</v>
       </c>
       <c r="M73" t="n">
         <v>1.32</v>
       </c>
       <c r="N73" t="n">
-        <v>2.39</v>
+        <v>4.12</v>
       </c>
       <c r="O73" t="n">
         <v>-1.59</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>7.99</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="H74" t="n">
-        <v>87.28</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I74" t="n">
         <v>86.96862733272202</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.99</v>
+        <v>-6.4</v>
       </c>
       <c r="L74" t="n">
-        <v>6.36</v>
+        <v>7.35</v>
       </c>
       <c r="M74" t="n">
         <v>0.47</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>6.39</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="H75" t="n">
-        <v>92.31</v>
+        <v>93.2</v>
       </c>
       <c r="I75" t="n">
         <v>92.44907852667089</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.23</v>
+        <v>-7.25</v>
       </c>
       <c r="L75" t="n">
-        <v>7.42</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M75" t="n">
         <v>0.72</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>5.85</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H76" t="n">
-        <v>103.51</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="I76" t="n">
         <v>100.7605649273877</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K76" t="n">
-        <v>11.06</v>
+        <v>5.91</v>
       </c>
       <c r="L76" t="n">
         <v>1.58</v>
@@ -4773,7 +5684,7 @@
         <v>1.11</v>
       </c>
       <c r="N76" t="n">
-        <v>2.17</v>
+        <v>4.64</v>
       </c>
       <c r="O76" t="n">
         <v>0.96</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>11.38</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46066</v>
+        <v>46069</v>
       </c>
       <c r="H77" t="n">
-        <v>94.03</v>
+        <v>100.52</v>
       </c>
       <c r="I77" t="n">
         <v>100.2674567481797</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K77" t="n">
-        <v>4.74</v>
+        <v>-1.83</v>
       </c>
       <c r="L77" t="n">
         <v>9.43</v>
@@ -4830,7 +5753,7 @@
         <v>2.13</v>
       </c>
       <c r="N77" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="O77" t="n">
         <v>-4.64</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>11.34</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H78" t="n">
-        <v>95.06</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>94.76231367767949</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K78" t="n">
-        <v>-5.43</v>
+        <v>-8.41</v>
       </c>
       <c r="L78" t="n">
-        <v>7.98</v>
+        <v>9.83</v>
       </c>
       <c r="M78" t="n">
         <v>4.5</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>10.64</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H79" t="n">
-        <v>94.92</v>
+        <v>99.22</v>
       </c>
       <c r="I79" t="n">
         <v>97.48109807510909</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K79" t="n">
-        <v>-3.1</v>
+        <v>-7.77</v>
       </c>
       <c r="L79" t="n">
-        <v>5.52</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M79" t="n">
         <v>3.81</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>12.01</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="H80" t="n">
-        <v>107.1</v>
+        <v>103.91</v>
       </c>
       <c r="I80" t="n">
         <v>106.1645533482858</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K80" t="n">
-        <v>7.94</v>
+        <v>4.73</v>
       </c>
       <c r="L80" t="n">
         <v>6.97</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>5</v>
+      </c>
+      <c r="U80" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>62</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105.4</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.2</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.53</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.77</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.8</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>43.71</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.8</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.279999999999999</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.43</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -10179,7 +11158,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.88</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="22">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="25">
@@ -10219,7 +11198,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="26">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.31</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="27">
@@ -10239,7 +11218,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.64</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="28">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
